--- a/registration_forms/050_iwoca_2013_camp_registration--registration_forms.xlsx
+++ b/registration_forms/050_iwoca_2013_camp_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>Main Page</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>main_page_section1</t>
+          <t>Main Page Section 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>captcha</t>
+          <t>CAPTCHA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Select One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>Select Multiple</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>captcha_response</t>
+          <t>CAPTCHA Response</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,13 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>main_page_section2</t>
+          <t>additional_section1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>main_page_section2</t>
+          <t>Additional Section 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>captcha</t>
+          <t>additional_section2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>captcha</t>
+          <t>Additional Section 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>additional_section3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Additional Section 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>message_box</t>
+          <t>Message Box</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>main_page_section3</t>
+          <t>additional_section3_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>main_page_section3</t>
+          <t>Additional Section3 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>terms</t>
+          <t>Terms</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,57 +1031,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>conditions</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'option_1'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1102,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'option_2'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'option_3'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'option_1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'option_2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'option_3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1187,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option_4',_'label':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'option_4', 'label': 'option_4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'option_5',_'label':_'option_5'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'option_5', 'label': 'option_5'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'label':_'agree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'label': 'agree'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>terms_and_conditions_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'disagree',_'label':_'disagree'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'disagree', 'label': 'disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
